--- a/7 Future comparisons/Bonaire/output/Rugosity_growth_param_0.5.xlsx
+++ b/7 Future comparisons/Bonaire/output/Rugosity_growth_param_0.5.xlsx
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.8749991867324</v>
+        <v>1.908845390176542</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.86518428043397</v>
+        <v>1.92885020732202</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.851491537915808</v>
+        <v>1.943034483544488</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.85534047880856</v>
+        <v>1.97151901206204</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.627099319317675</v>
+        <v>1.713734314677676</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.652067518649414</v>
+        <v>1.753785918099239</v>
       </c>
     </row>
     <row r="9">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.538383585921651</v>
+        <v>1.624070532420547</v>
       </c>
     </row>
     <row r="10">
@@ -504,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.525624701454723</v>
+        <v>1.602787555770905</v>
       </c>
     </row>
     <row r="11">
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.557936776130787</v>
+        <v>1.640662728356776</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.598061022751344</v>
+        <v>1.68864408151425</v>
       </c>
     </row>
     <row r="13">
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.656065720536129</v>
+        <v>1.754352913264195</v>
       </c>
     </row>
     <row r="14">
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.708067352140944</v>
+        <v>1.813248421438073</v>
       </c>
     </row>
     <row r="15">
@@ -544,7 +544,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.774133120438689</v>
+        <v>1.886487421564857</v>
       </c>
     </row>
     <row r="16">
@@ -552,7 +552,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.827117061307437</v>
+        <v>1.946451506172642</v>
       </c>
     </row>
     <row r="17">
@@ -560,7 +560,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.893359246722393</v>
+        <v>2.017618748603856</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.949282691406802</v>
+        <v>2.077977594498041</v>
       </c>
     </row>
     <row r="19">
@@ -576,7 +576,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.006432850464371</v>
+        <v>2.139191255548708</v>
       </c>
     </row>
     <row r="20">
@@ -584,7 +584,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.052539845014411</v>
+        <v>2.188482633067167</v>
       </c>
     </row>
     <row r="21">
@@ -592,7 +592,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.09951016984236</v>
+        <v>2.238369125961266</v>
       </c>
     </row>
     <row r="22">
@@ -600,7 +600,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>2.14545129713602</v>
+        <v>2.284588827753609</v>
       </c>
     </row>
     <row r="23">
@@ -608,7 +608,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>2.183440369145294</v>
+        <v>2.32459821712975</v>
       </c>
     </row>
     <row r="24">
@@ -616,7 +616,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>2.228651406995971</v>
+        <v>2.368131239850893</v>
       </c>
     </row>
     <row r="25">
@@ -624,7 +624,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>2.256091985749962</v>
+        <v>2.396539972809898</v>
       </c>
     </row>
     <row r="26">
@@ -632,7 +632,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>2.29336444869398</v>
+        <v>2.431935901140414</v>
       </c>
     </row>
     <row r="27">
@@ -640,7 +640,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>2.323522593450619</v>
+        <v>2.460021239161789</v>
       </c>
     </row>
     <row r="28">
@@ -648,7 +648,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>2.34442597047818</v>
+        <v>2.479688257054586</v>
       </c>
     </row>
   </sheetData>
